--- a/ragas_gpt4o_report.xlsx
+++ b/ragas_gpt4o_report.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>**拇趾外翻**是指腳背第一掌骨與大拇趾之間的關節呈現外凸彎曲的變形，典型症狀包括關節外凸、其餘腳趾的擠壓變形，以及足部疼痛。**遺傳因素**是導致此症的最大成因，因足部骨骼形狀（腳型）主要遺傳自父母或家族長輩，許多患者在小時候即有拇趾關節彎曲的現象，若未進行腳趾肌肉鍛鍊，長大後關節彎曲會加劇，甚至演變成嚴重的腳趾變形或疊趾。此外，拇趾外翻的程度可依**HVA（Hallux Valgus Angle）**與**IMA（Intermetatarsal Angle）**角度分為正常、輕微、中度及嚴重四級，其中正常範圍為HVA&lt;15度、IMA&lt;9度，嚴重程度則為HVA&gt;40度、IMA&gt;18度。</t>
+          <t>**拇趾外翻**為腳背第一掌骨與大拇趾關節外凸彎曲的變形，常伴關節外凸、腳趾擠壓變形及疼痛，主因為**遺傳**的腳型及未進行肌肉鍛鍊所致。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4195718108790811</v>
+        <v>0.5871239450936215</v>
       </c>
       <c r="G2" t="n">
-        <v>0.99999999995</v>
+        <v>0.699999999965</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -512,12 +512,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['扁平足的後天性成因包括：1.足部太早承重，讓未滿十個月的幼兒使用螃蟹車或學步車，使足部在不穩定狀態下開始承受重量，導致足弓發育遲緩；2.肌肉韌帶無力，幼兒型扁平足大多屬小腿後脛肌無力，促使足弓塌陷扁平；3.發展遲緩或骨骼神經病變，早產兒與幼兒整體性發展遲緩或神經病變會使足弓發育延緩；4.錯誤姿勢，長時間跪坐玩玩具、看電視會造成足弓發展受阻與X形腿產生；5.肥胖或懷孕，體重過重會讓足部壓力增加，成人在懷孕後或中老年時期足弓都會變得較扁平。', '扁平足的先天性原因包括：1.先天性跗骨黏合或附生舟狀骨，最常見是踵骨和距骨的黏合，會造成「僵硬型扁平足」；2.先天性韌帶鬆弛，可能是全身性現象，或因懷孕後期嬰幼兒在子宮內肢體活動不靈活（俗稱「壓胎」）造成；3.遺傳因素，研究顯示扁平足具有遺傳性，扁平足的父母較可能生出扁平足子女；4.性別差異，國外文獻顯示女生略多於男生，但台灣研究發現男生比率略高於女生。', '扁平足後天原因之一：現今父母或保母在幼兒正經爬行階段，害怕地板骯髒或安全考量與照顧方便，即讓未滿十個月之幼兒使用螃蟹車或學步車，讓足部還在不穩定狀態便開始承受重量，以致足弓發育遲緩。', '扁平足先天原因之一：有些小朋友先天有跗骨黏合的現象，最常見是踵骨和距骨的黏合，此種黏合會造成「僵硬型扁平足」。', '扁平足是指內側足弓過低甚至塌陷的足型。人體足部是最複雜的結構之一，由26塊骨骼、57個可動或微動關節、108條韌帶及32條肌肉組成，並形成三個縱橫弓與一個假性小橫弓，提供穩定度及活動度，使足部能承受全身重量的負荷。', '成人扁平足的足部失去吸震、緩衝、減壓之作用，較會引起走遠路或跑步時下肢易疲勞、足底肌膜炎、大腳趾變形關節疼痛等問題', '先天性跗骨黏合或附生舟狀骨，有些小朋友先天有跗骨黏合的現象，最常見是踵骨和距骨的黏合，此種黏合會造成僵硬型扁平足', '成人扁平足失去吸震、緩衝、減壓作用，較會引起走遠路或跑步時下肢易疲勞、足底肌膜炎、大腳趾變形關節疼痛、膝關節炎、踝關節扭傷、腰酸背痛、脊柱側彎、骨盆歪斜、長短腳等問題。如果沒有從足部著手改善，常常無法徹底解決根本問題，正如「腳不對、整個人都不對」，可見人體地基足部的重要性。']</t>
+          <t>['內側足弓過低，甚至是塌陷，稱之為扁平足', '成人扁平足的足部失去吸震、緩衝、減壓之作用，較會引起走遠路或跑步時下肢易疲勞、足底肌膜炎、大腳趾變形關節疼痛等問題', '成人扁平足失去吸震、緩衝、減壓作用，較會引起走遠路或跑步時下肢易疲勞、足底肌膜炎、大腳趾變形關節疼痛、膝關節炎、踝關節扭傷、腰酸背痛、脊柱側彎、骨盆歪斜、長短腳等問題。如果沒有從足部著手改善，常常無法徹底解決根本問題，正如「腳不對、整個人都不對」，可見人體地基足部的重要性。', '幼兒型扁平足大部份屬小腿後脛肌無力，促使足弓塌陷扁平', '扁平足的後天性成因包括：1.足部太早承重，讓未滿十個月的幼兒使用螃蟹車或學步車，使足部在不穩定狀態下開始承受重量，導致足弓發育遲緩；2.肌肉韌帶無力，幼兒型扁平足大多屬小腿後脛肌無力，促使足弓塌陷扁平；3.發展遲緩或骨骼神經病變，早產兒與幼兒整體性發展遲緩或神經病變會使足弓發育延緩；4.錯誤姿勢，長時間跪坐玩玩具、看電視會造成足弓發展受阻與X形腿產生；5.肥胖或懷孕，體重過重會讓足部壓力增加，成人在懷孕後或中老年時期足弓都會變得較扁平。', '有些小朋友的體重過重也會讓足部的壓力增加，成人在懷孕後或中老年時期足弓皆會變的較扁平', '一旦影響腿型與走路的方式，就會進而影響到足弓的發育，常會合併扁平足與足跟歪斜問題', '大多數的扁平足不一定有症狀，少數會因扁平足或整體性發育遲緩與韌帶鬆弛，使跑跳、平衡等粗動作受影響而常跌倒']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>**扁平足**的形成原因可分為先天性與後天性兩大類。先天性原因主要包括**跗骨黏合**或**附生舟狀骨**，例如最常見的**踵骨與距骨黏合**會導致「僵硬型扁平足」；此外，**先天性韌帶鬆弛**可能為全身性現象，或因懷孕後期子宮內肢體活動受限（壓胎）所致；**遺傳因素**亦被研究證實，扁平足父母較易生出相同子女；**性別差異**方面，雖國外文獻顯示女性較多，但台灣研究則發現男性比率略高。後天性原因包括**足部過早承重**，如未滿十個月幼兒過早使用學步車，使足弓發育受阻；**肌肉韌帶無力**，如小腿後脛肌無力易導致足弓塌陷；**發展遲緩或神經病變**會延緩足弓發育；**錯誤姿勢**如長時間跪坐可能引發X形腿與足弓變形；**肥胖或懷孕**則因體重增加使足部壓力上升，成人懷孕或中老年時期易出現足弓變扁。這些因素共同作用，影響足部結構與功能，進而形成扁平足。</t>
+          <t>**扁平足**的成因包括**遺傳因素**、**肌肉韌帶無力**（如小腿後脛肌無力）、**足部過早承重**（如學步車使用）、**錯誤姿勢**（如長時間跪坐）、**肥胖或懷孕**導致足部壓力增加，以及**發展遲緩或神經病變**。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8562291394962794</v>
+        <v>0.7484137457552797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8928571428348213</v>
+        <v>0.19999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -546,12 +546,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['O形腿的形成與高弓足有絕對關係，就是因為高弓足的內側足弓過高，才會使得兩腳膝蓋向外擠壓', '高弓足較嚴重的那一邊往往就是腿部較短那邊', '長時間處在跪坐的姿勢玩玩具、看電視，也會造成足弓發展受阻與X形腿的產生', '一旦影響腿型與走路的方式，就會進而影響到足弓的發育，常會合併扁平足與足跟歪斜問題', '高弓足除了讓腳部不適，容易伴隨肩頸痠痛，腳跟及蹠骨突出部位長繭，還可能造成足底筋膜炎、蹠骨炎、長短腿、脊椎側彎等問題', '高弓足的人因為足踝向外傾，所以產生錯誤的足部生物力學，造成小腿內外側出力不均，外側肌肉長期被拉扯肌耐力變差', '高弓足的雙腳因體重分部不均，走路方式容易外旋、穩定度不佳，其他關節較易產生角度過大的傷害', '高弓足對久站影響：高弓足的人因為足踝向外傾，所以產生錯誤的足部生物力學，造成小腿內外側出力不均，外側肌肉長期被拉扯肌耐力變差，因此不耐久走、久站']</t>
+          <t>['O形腿的形成與高弓足有絕對關係，就是因為高弓足的內側足弓過高，才會使得兩腳膝蓋向外擠壓', '長時間處在跪坐的姿勢玩玩具、看電視，也會造成足弓發展受阻與X形腿的產生', '高弓足較嚴重的那一邊往往就是腿部較短那邊', '高弓足除了讓腳部不適，容易伴隨肩頸痠痛，腳跟及蹠骨突出部位長繭，還可能造成足底筋膜炎、蹠骨炎、長短腿、脊椎側彎等問題', 'O型腿的臨床表徵是指膝蓋向內翻、髕骨朝內轉、兩腳踝碰在一起兩膝內側卻留有空隙', '高弓足可以明顯看到拱起來的腳背，腳掌心距離地面的空隙也更大，高足弓多發生於女性', '一旦影響腿型與走路的方式，就會進而影響到足弓的發育，常會合併扁平足與足跟歪斜問題', '高弓足的人因為足踝向外傾，所以產生錯誤的足部生物力學，造成小腿內外側出力不均，外側肌肉長期被拉扯肌耐力變差']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>**高弓足與O型腿之間確實存在密切關係**，這是因為高弓足的內側足弓過高，會導致兩腳膝蓋向外擠壓，進而形成O形腿的特徵。此外，高弓足較嚴重的那一邊往往就是腿部較短的部位，這種長短腿的現象會進一步加劇腿型的異常。**O型腿的形成與高弓足有絕對關係**，不僅影響腿型，還可能導致走路方式改變，進而影響足弓的發育，常合併扁平足與足跟歪斜問題。長期下來，高弓足會造成足部生物力學失衡，使小腿內外側出力不均，外側肌肉長期被拉扯而肌耐力變差，甚至影響久站與久走的耐受性。因此，高弓足不僅與O型腿直接相關，也會引發一系列足部及關節的後續問題。</t>
+          <t>**高弓足**與**O型腿**有絕對關聯，因高弓足內側足弓過高，導致兩膝向外擠壓，形成膝蓋內翻的**O型腿**表徵。此外，足踝外傾影響生物力學，加劇腿型異常。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3924784190561751</v>
+        <v>0.5185449257534516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5873015872820105</v>
+        <v>0.62499999996875</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -580,12 +580,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['造成小孩走路內八通常有三個原因：前足內收、脛骨內旋、髖關節過度內傾', '內八通常有三個原因，即是前足內收、脛骨內旋、髖關節過度內傾，需經醫療專業人員仔細檢查評估', '走路內八常見於學齡期孩童，當發現孩童在行走時兩腳往內撇，並且走路或跑步時常常摔倒受傷', '內八的步態為何：我們觀察有些孩子走路常跌倒，仔細看他走路的步態會發現兩腳容易碰撞而引起跌倒', '內八是因脛骨骨骼生理性發育正常之現象，也會自行復原', '3歲左右，大腿骨會由出生時的外轉逐漸內轉，若內轉過多就會形成內八', '內八則是方向往內偏移前進，因此容易於行走中雙腳相絆而造成跌倒', '兒童出生後18~24個月間的內八是生理發育正常之現象']</t>
+          <t>['造成小孩走路內八通常有三個原因：前足內收、脛骨內旋、髖關節過度內傾', '內八通常有三個原因，即是前足內收、脛骨內旋、髖關節過度內傾，需經醫療專業人員仔細檢查評估', '走路內八常見於學齡期孩童，當發現孩童在行走時兩腳往內撇，並且走路或跑步時常常摔倒受傷', '內八的步態為何：我們觀察有些孩子走路常跌倒，仔細看他走路的步態會發現兩腳容易碰撞而引起跌倒', '兒童出生後18~24個月間的內八是生理發育正常之現象', '兒童內八現象於臨床上是很常見的，2~5歲約10%會有這樣的問題', '孩童年齡若超過3歲後仍有脛骨內旋而產生內八，且經醫療專業人員檢查測量脛骨小腿與足的角度超過-45度，即須處理治療', '內八則是方向往內偏移前進，因此容易於行走中雙腳相絆而造成跌倒']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>兒童出現內八步態的原因主要包括**前足內收**、**脛骨內旋**以及**髖關節過度內傾**，這些因素會影響足部與下肢的正常對齊。此外，**內八**是因脛骨骨骼生理性發育正常之現象，也會自行復原，尤其在**3歲左右**，大腿骨會由出生時的外轉逐漸內轉，若內轉過多就會形成內八。此現象常見於學齡期孩童，當發現孩童在行走時兩腳往內撇，且走路或跑步時容易跌倒受傷，進一步觀察其步態會發現雙腳易碰撞而引起跌倒。值得注意的是，**18~24個月間**的內八屬於生理發育正常之現象，通常會隨時間自然改善。</t>
+          <t>**內八**步態常見原因包括**前足內收**、**脛骨內旋**以及**髖關節過度內傾**，需經專業檢查評估。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4646488851317489</v>
+        <v>0.605571844863642</v>
       </c>
       <c r="G5" t="n">
-        <v>0.99999999995</v>
+        <v>0.8095238094968253</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -614,12 +614,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['糖尿病鞋設計要求：鞋前楦頭必須加寬且加高（在腳趾的空間），前楦頭之鋼保，必須加硬防止碰撞，形成保護。', '糖尿病患者鞋款特性：糖尿病鞋款應具備鞋前楦頭加寬加高，提供腳趾舒適的伸展空間；前楦頭加港寶，防撞及保護', '在糖尿病鞋保護下，避免足部因碰撞或外傷而產生傷口', '糖尿病患者鞋墊選擇：鞋墊應據有減壓功能，像是針對有傷口的部位拆除，降低對傷口的壓力與磨擦', '糖尿病患者足部照護原則：糖尿病患者足部照護要點包括初次穿新鞋子，不要穿太久，不可以赤腳走路，避免在任何地方赤腳走路', '可移動式的糖尿病專用減壓鞋墊，具有前楦翹板Rocker設計的鞋，去降低足部的壓力、改善疼痛', '鞋內盡量減少縫線及材料接縫處、避免造成壓迫，鞋內材質宜為真皮或軟質布料', '因第二趾過長、鎚狀趾、橫弓塌陷、腳趾過度背屈、常見於穿高跟鞋之女性及空凹腳']</t>
+          <t>['糖尿病鞋設計要求：鞋前楦頭必須加寬且加高（在腳趾的空間），前楦頭之鋼保，必須加硬防止碰撞，形成保護。', '糖尿病患者鞋款特性：糖尿病鞋款應具備鞋前楦頭加寬加高，提供腳趾舒適的伸展空間；前楦頭加港寶，防撞及保護', '在糖尿病鞋保護下，避免足部因碰撞或外傷而產生傷口', '糖尿病患者鞋墊選擇：鞋墊應據有減壓功能，像是針對有傷口的部位拆除，降低對傷口的壓力與磨擦', '糖尿病患者足部照護原則：糖尿病患者足部照護要點包括初次穿新鞋子，不要穿太久，不可以赤腳走路，避免在任何地方赤腳走路', '特殊之足部輔具如糖尿病鞋及特製鞋墊，在保護糖尿病足上就顯的非常重要，除了能有效分散壓力、減少壓瘡', '可移動式的糖尿病專用減壓鞋墊，具有前楦翹板Rocker設計的鞋，去降低足部的壓力、改善疼痛', '鞋內盡量減少縫線及材料接縫處、避免造成壓迫，鞋內材質宜為真皮或軟質布料']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>糖尿病患者在選擇鞋子時應注意**鞋款設計**、**材質選擇**及**足部適配性**等多項事項。首先，**鞋前楦頭必須加寬加高**，以提供腳趾舒適的伸展空間，並搭配**加硬的鋼保結構**，防止碰撞傷害，降低足部受傷風險。此外，**鞋內應減少縫線及材料接縫處**，避免造成壓迫，材質宜選用**真皮或軟質布料**，以提升舒適度與透氣性。為進一步降低足部壓力，可選擇具**前楦翹板Rocker設計**的鞋款，並搭配**可移動式的減壓鞋墊**，針對傷口部位進行壓力分散與摩擦減緩。同時，**足部照護原則**亦強調，初次穿新鞋子不宜過久，且應避免赤腳行走，以預防足部受損。針對常見的**第二趾過長、鎚狀趾、橫弓塌陷**等足部結構問題，鞋款設計需具備足夠的空間與支撐性，尤其需注意**空凹腳**患者的特殊需求，確保鞋子能有效保護足部並促進健康。</t>
+          <t>糖尿病患者選鞋應注意**鞋前楦頭加寬加高**以提供足夠空間，**加硬鋼保**防碰撞，**減壓鞋墊**降低傷口壓力，並選用**真皮或軟質布料**減少摩擦，避免**縫線接縫**及赤腳行走。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -631,13 +631,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5417933754778627</v>
+        <v>0.4985729135500284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4206349206208995</v>
+        <v>0.37499999998125</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
